--- a/题库/PY选择题练习.xlsx
+++ b/题库/PY选择题练习.xlsx
@@ -378,7 +378,7 @@
     <t>&gt;&gt;&gt; 'ABCD' == 'abcd'.upper()</t>
   </si>
   <si>
-    <t>&gt;&gt;&gt; 'c' &lt; 'a'</t>
+    <t>&gt;&gt;&gt; '' &lt; 'a'</t>
   </si>
   <si>
     <t>&gt;&gt;&gt; 'python' &lt; 'pypi'</t>
@@ -898,6 +898,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下列程序的输出结果是</t>
     </r>
     <r>
